--- a/app/templates/copias/Template_GranSuelo-copia.xlsx
+++ b/app/templates/copias/Template_GranSuelo-copia.xlsx
@@ -21706,7 +21706,11 @@
       <c r="G11" s="782"/>
       <c r="H11" s="781"/>
       <c r="I11" s="782"/>
-      <c r="J11" s="686"/>
+      <c r="J11" s="686" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K11" s="387"/>
       <c r="L11" s="685"/>
       <c r="M11" s="685"/>
@@ -22787,8 +22791,10 @@
       <c r="Q2" s="323" t="s">
         <v>362</v>
       </c>
-      <c r="R2" s="531" t="s">
-        <v>442</v>
+      <c r="R2" s="531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S2" s="386"/>
       <c r="T2" s="279"/>
@@ -22812,15 +22818,19 @@
       <c r="Q3" s="323" t="s">
         <v>363</v>
       </c>
-      <c r="R3" s="531" t="s">
-        <v>442</v>
+      <c r="R3" s="531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S3" s="386"/>
       <c r="U3" s="562" t="s">
         <v>467</v>
       </c>
-      <c r="V3" s="542" t="s">
-        <v>442</v>
+      <c r="V3" s="542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="W3" s="284">
         <f>+FORMATO!J11</f>
